--- a/artfynd/A 31507-2025 artfynd.xlsx
+++ b/artfynd/A 31507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91691529</v>
+        <v>91691091</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389732.5876090154</v>
+        <v>389819.380516899</v>
       </c>
       <c r="R2" t="n">
-        <v>6263080.132192697</v>
+        <v>6263310.871726973</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
+          <t>2017-07-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskogssluttning</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,6 +789,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91691529</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95717</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Perstorps skog, vid Hjörneredssjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>389732.5876090154</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6263080.132192697</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ränneslöv</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jan-Erik Hederås</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jan-Erik Hederås, Gunilla Hederås</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31507-2025 artfynd.xlsx
+++ b/artfynd/A 31507-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91691529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,8 +882,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91691091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>